--- a/VALIDATION/CAS SFS02/Cas SFS02.xlsx
+++ b/VALIDATION/CAS SFS02/Cas SFS02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\RAID 1\LOGICIELS\CTICM AM - POUTRE MIXTE\DEV23\VALIDATION\CAS SFS02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAF30192-FD13-4E86-B342-38AC6A211A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8517F67-C611-468C-958A-29FCCE0E8698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -59,6 +59,7 @@
     <definedName name="hb">Feuil1!$D$12</definedName>
     <definedName name="Ht">Feuil1!$D$15</definedName>
     <definedName name="hw">Feuil1!$D$8</definedName>
+    <definedName name="hwe">Feuil1!$N$45</definedName>
     <definedName name="hwP">Feuil1!$D$16</definedName>
     <definedName name="IncertieCM">Feuil1!$N$29</definedName>
     <definedName name="InertieY_MM4">Feuil1!$N$28</definedName>
@@ -134,7 +135,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="156">
   <si>
     <t>hw</t>
   </si>
@@ -599,6 +600,9 @@
   </si>
   <si>
     <t>w-inf</t>
+  </si>
+  <si>
+    <t>Hauteur de l'élément âme</t>
   </si>
 </sst>
 </file>
@@ -611,7 +615,7 @@
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -631,6 +635,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -903,7 +914,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1152,6 +1163,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2381,7 +2398,7 @@
       </c>
       <c r="J36" s="52">
         <f>MEd_U1/MplRd</f>
-        <v>0.68444711032113492</v>
+        <v>0.74028353165455463</v>
       </c>
       <c r="M36" s="41" t="s">
         <v>92</v>
@@ -2606,13 +2623,23 @@
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
-      <c r="M45" t="s">
-        <v>152</v>
+      <c r="M45" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="N45" s="6">
+        <f>hwP</f>
+        <v>206</v>
+      </c>
+      <c r="O45" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C46" s="3"/>
       <c r="D46" s="4"/>
+      <c r="M46" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="47" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C47" s="3" t="s">
@@ -2628,6 +2655,10 @@
         <v>48</v>
       </c>
       <c r="N47" s="52">
+        <f>(P35+P36+P37-P40)/2/P37</f>
+        <v>5.2838812974922822E-2</v>
+      </c>
+      <c r="Q47" s="52">
         <f>(P35+P36+P37-P40)/2/P37</f>
         <v>5.2838812974922822E-2</v>
       </c>
@@ -2639,11 +2670,15 @@
         <v>49</v>
       </c>
       <c r="N48" s="53">
-        <f>pANP*(hw-rr)</f>
-        <v>17.172614216849919</v>
+        <f>pANP*(hwe)</f>
+        <v>10.884795472834101</v>
       </c>
       <c r="O48" t="s">
         <v>2</v>
+      </c>
+      <c r="S48">
+        <f>(1-pANP)*(hwP-rr)/2</f>
+        <v>84.770926238744408</v>
       </c>
     </row>
     <row r="49" spans="3:21" x14ac:dyDescent="0.25">
@@ -2674,6 +2709,10 @@
       </c>
       <c r="E50" t="s">
         <v>63</v>
+      </c>
+      <c r="S50">
+        <f>hwP-rr</f>
+        <v>179</v>
       </c>
     </row>
     <row r="51" spans="3:21" x14ac:dyDescent="0.25">
@@ -2733,11 +2772,14 @@
       </c>
       <c r="P52" s="67">
         <f>O52-zANP</f>
-        <v>200.82738578315008</v>
+        <v>207.1152045271659</v>
       </c>
       <c r="Q52" s="87">
         <f>N52*ABS(P52/1000)</f>
-        <v>498.85522628534477</v>
+        <v>514.47416804548004</v>
+      </c>
+      <c r="R52" s="102">
+        <v>514.47</v>
       </c>
       <c r="T52" s="101">
         <f>(1-T53)-T53</f>
@@ -2779,11 +2821,14 @@
       </c>
       <c r="P53" s="68">
         <f>O53-zANP</f>
-        <v>182.79645143161477</v>
+        <v>189.08427017563059</v>
       </c>
       <c r="Q53" s="89">
         <f t="shared" ref="Q53:Q56" si="9">N53*ABS(P53/1000)</f>
-        <v>19.732304747973814</v>
+        <v>20.411055099445264</v>
+      </c>
+      <c r="R53" s="102">
+        <v>20.41</v>
       </c>
       <c r="T53" s="101">
         <f>1-T54</f>
@@ -2808,17 +2853,18 @@
         <v>908.74906508527522</v>
       </c>
       <c r="O54" s="88">
-        <f>(hw-rr)-(1-pANP)*(hw-rr)/2</f>
-        <v>171.08630710842496</v>
+        <f>(hwe)-(1-pANP)*(hwe)/2</f>
+        <v>108.44239773641705</v>
       </c>
       <c r="P54" s="68">
         <f>O54-zANP</f>
-        <v>153.91369289157504</v>
-      </c>
-      <c r="Q54" s="89">
+        <v>97.55760226358295</v>
+      </c>
+      <c r="Q54" s="103">
         <f t="shared" si="9"/>
-        <v>139.86892451904097</v>
-      </c>
+        <v>88.655379848992141</v>
+      </c>
+      <c r="R54" s="102"/>
       <c r="S54" s="6">
         <v>105</v>
       </c>
@@ -2857,16 +2903,19 @@
         <v>50.69593491472483</v>
       </c>
       <c r="O55" s="88">
-        <f>(pANP)*(hw-rr)/2</f>
-        <v>8.5863071084249594</v>
+        <f>(pANP)*(hwe)/2</f>
+        <v>5.4423977364170506</v>
       </c>
       <c r="P55" s="68">
         <f>O55-zANP</f>
-        <v>-8.5863071084249594</v>
-      </c>
-      <c r="Q55" s="89">
+        <v>-5.4423977364170506</v>
+      </c>
+      <c r="Q55" s="103">
         <f t="shared" si="9"/>
-        <v>0.4352908663265509</v>
+        <v>0.27590744142544454</v>
+      </c>
+      <c r="R55" s="102">
+        <v>88.93</v>
       </c>
       <c r="U55" s="75">
         <f>T54*P37</f>
@@ -2890,11 +2939,14 @@
       </c>
       <c r="P56" s="73">
         <f>O56-zANP</f>
-        <v>-27.172614216849919</v>
+        <v>-20.884795472834099</v>
       </c>
       <c r="Q56" s="91">
         <f t="shared" si="9"/>
-        <v>93.745519048132209</v>
+        <v>72.052544381277642</v>
+      </c>
+      <c r="R56" s="102">
+        <v>72.040000000000006</v>
       </c>
       <c r="U56" s="75"/>
     </row>
@@ -2904,7 +2956,7 @@
       <c r="J57" s="4"/>
       <c r="Q57" s="85">
         <f>SUM(Q52:Q56)</f>
-        <v>752.63726546681835</v>
+        <v>695.86905481662052</v>
       </c>
       <c r="U57" s="75">
         <f>U54-U55</f>
@@ -2924,7 +2976,7 @@
       </c>
       <c r="Q59" s="76">
         <f>Q57</f>
-        <v>752.63726546681835</v>
+        <v>695.86905481662052</v>
       </c>
       <c r="R59" t="s">
         <v>18</v>

--- a/VALIDATION/CAS SFS02/Cas SFS02.xlsx
+++ b/VALIDATION/CAS SFS02/Cas SFS02.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\RAID 1\LOGICIELS\CTICM AM - POUTRE MIXTE\DEV23\VALIDATION\CAS SFS02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8517F67-C611-468C-958A-29FCCE0E8698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48A03D8D-4A2E-4712-98CD-DA4CC2A9511D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
-    <sheet name="Section élastique" sheetId="3" r:id="rId2"/>
+    <sheet name="Flexion locale" sheetId="3" r:id="rId2"/>
     <sheet name="Param" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
@@ -30,14 +30,14 @@
     <definedName name="Bac_Hp">Feuil1!#REF!</definedName>
     <definedName name="Bac_Mu">Feuil1!#REF!</definedName>
     <definedName name="Bac_t">Feuil1!#REF!</definedName>
-    <definedName name="bAppMin">Feuil1!#REF!</definedName>
+    <definedName name="bAppMin">Feuil1!$D$43</definedName>
     <definedName name="BetaW">Feuil1!#REF!</definedName>
     <definedName name="bf">Feuil1!$D$6</definedName>
     <definedName name="d_1">Feuil1!$D$29</definedName>
     <definedName name="d_2">Feuil1!$D$30</definedName>
-    <definedName name="dApp">'Section élastique'!$D$15</definedName>
-    <definedName name="df">'Section élastique'!$D$23</definedName>
-    <definedName name="dp">'Section élastique'!$D$19</definedName>
+    <definedName name="dApp">'Flexion locale'!$D$15</definedName>
+    <definedName name="df">'Flexion locale'!$D$23</definedName>
+    <definedName name="dp">'Flexion locale'!$D$19</definedName>
     <definedName name="dW">Feuil1!$D$9</definedName>
     <definedName name="E">Feuil1!$D$28</definedName>
     <definedName name="Elan">Feuil1!#REF!</definedName>
@@ -86,6 +86,7 @@
     <definedName name="non">Param!$C$3</definedName>
     <definedName name="oui">Param!$C$2</definedName>
     <definedName name="pANP">Feuil1!$N$47</definedName>
+    <definedName name="pAnpLoc">'Flexion locale'!$M$38</definedName>
     <definedName name="PhiLT">Feuil1!#REF!</definedName>
     <definedName name="Pl_b">Feuil1!$D$13</definedName>
     <definedName name="Pl_t">Feuil1!$D$14</definedName>
@@ -112,7 +113,9 @@
     <definedName name="VEdG">Feuil1!$J$14</definedName>
     <definedName name="VRd">Feuil1!#REF!</definedName>
     <definedName name="zANP">Feuil1!$N$48</definedName>
+    <definedName name="zANPloc">'Flexion locale'!$M$39</definedName>
     <definedName name="zG">Feuil1!$N$27</definedName>
+    <definedName name="zSup">'Flexion locale'!$M$14</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -135,7 +138,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="166">
   <si>
     <t>hw</t>
   </si>
@@ -603,6 +606,36 @@
   </si>
   <si>
     <t>Hauteur de l'élément âme</t>
+  </si>
+  <si>
+    <t>bAppMin</t>
+  </si>
+  <si>
+    <t>dbt</t>
+  </si>
+  <si>
+    <t>mybtEd</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>fy</t>
+  </si>
+  <si>
+    <t>mybtRd</t>
+  </si>
+  <si>
+    <t>EtaM</t>
+  </si>
+  <si>
+    <t>PsiY</t>
+  </si>
+  <si>
+    <t>Propriétés plastiques modifiées</t>
+  </si>
+  <si>
+    <t>zSup</t>
   </si>
 </sst>
 </file>
@@ -914,7 +947,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1167,6 +1200,15 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1508,7 +1550,7 @@
       </c>
       <c r="I6" s="95">
         <f>D55</f>
-        <v>14.364851987848585</v>
+        <v>13.481951987848586</v>
       </c>
       <c r="J6" t="s">
         <v>7</v>
@@ -1674,7 +1716,7 @@
       </c>
       <c r="J13" s="9">
         <f>qG*LL^2/8</f>
-        <v>114.91881590278868</v>
+        <v>107.85561590278868</v>
       </c>
       <c r="K13" s="12" t="s">
         <v>18</v>
@@ -1696,7 +1738,7 @@
       </c>
       <c r="J14" s="80">
         <f>qG*LL/2</f>
-        <v>57.45940795139434</v>
+        <v>53.927807951394342</v>
       </c>
       <c r="K14" s="15" t="s">
         <v>8</v>
@@ -2004,7 +2046,7 @@
       </c>
       <c r="J23" s="48">
         <f>GammaG*MEdG+GammaQ*(MEd_Q1+Psi_0*MEd_Q2)</f>
-        <v>515.14040146876471</v>
+        <v>505.60508146876475</v>
       </c>
       <c r="K23" s="31" t="s">
         <v>18</v>
@@ -2050,7 +2092,7 @@
       </c>
       <c r="J24" s="48">
         <f>GammaG*VEdG+GammaQ*(VEd_Q1+Psi_0*VEd_Q2)</f>
-        <v>257.57020073438235</v>
+        <v>252.80254073438238</v>
       </c>
       <c r="K24" s="34" t="s">
         <v>8</v>
@@ -2082,7 +2124,7 @@
       </c>
       <c r="J25" s="48">
         <f>GammaG*MEdG+GammaQ*(Psi_0*MEd_Q1+MEd_Q2)</f>
-        <v>407.14040146876471</v>
+        <v>397.60508146876475</v>
       </c>
       <c r="K25" s="37" t="s">
         <v>18</v>
@@ -2104,7 +2146,7 @@
       </c>
       <c r="J26" s="48">
         <f>GammaG*VEdG+GammaQ*(Psi_0*VEd_Q1+VEd_Q2)</f>
-        <v>203.57020073438235</v>
+        <v>198.80254073438238</v>
       </c>
       <c r="K26" s="40" t="s">
         <v>8</v>
@@ -2267,7 +2309,7 @@
       </c>
       <c r="J30" s="54">
         <f>GammaG*qG+GammaQ*(qQ_1)</f>
-        <v>64.392550183595588</v>
+        <v>63.200635183595594</v>
       </c>
       <c r="K30" t="s">
         <v>7</v>
@@ -2398,7 +2440,7 @@
       </c>
       <c r="J36" s="52">
         <f>MEd_U1/MplRd</f>
-        <v>0.74028353165455463</v>
+        <v>0.72658078121034531</v>
       </c>
       <c r="M36" s="41" t="s">
         <v>92</v>
@@ -2444,7 +2486,7 @@
       </c>
       <c r="J37" s="52">
         <f>VEd_U1/Q60</f>
-        <v>0.33123760419191417</v>
+        <v>0.32510635037645363</v>
       </c>
       <c r="M37" s="41" t="s">
         <v>27</v>
@@ -2572,7 +2614,7 @@
         <v>101</v>
       </c>
       <c r="D41" s="6">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="E41" t="s">
         <v>2</v>
@@ -2592,15 +2634,22 @@
       </c>
       <c r="D42" s="77">
         <f>td-(tPred-tJoint)</f>
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="E42" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="43" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="C43" s="3"/>
-      <c r="D43" s="4"/>
+      <c r="C43" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D43" s="6">
+        <v>50</v>
+      </c>
+      <c r="E43" t="s">
+        <v>2</v>
+      </c>
       <c r="M43" s="3" t="s">
         <v>81</v>
       </c>
@@ -2687,7 +2736,7 @@
       </c>
       <c r="D49" s="47">
         <f>td*(d_1+d_2)/2000</f>
-        <v>0.52200000000000002</v>
+        <v>0.48599999999999999</v>
       </c>
       <c r="E49" t="s">
         <v>66</v>
@@ -2705,7 +2754,7 @@
       </c>
       <c r="D50" s="9">
         <f>Ac*rhoC</f>
-        <v>1305</v>
+        <v>1215</v>
       </c>
       <c r="E50" t="s">
         <v>63</v>
@@ -2721,7 +2770,7 @@
       </c>
       <c r="D51" s="9">
         <f>D50*9.81/1000</f>
-        <v>12.802050000000001</v>
+        <v>11.919150000000002</v>
       </c>
       <c r="E51" t="s">
         <v>7</v>
@@ -2816,7 +2865,7 @@
         <v>107.94686982944954</v>
       </c>
       <c r="O53" s="88">
-        <f t="shared" ref="O53:O55" si="8">Q36</f>
+        <f t="shared" ref="O53" si="8">Q36</f>
         <v>199.96906564846469</v>
       </c>
       <c r="P53" s="68">
@@ -2883,7 +2932,7 @@
       </c>
       <c r="D55" s="81">
         <f>SUM(D51,D53)</f>
-        <v>14.364851987848585</v>
+        <v>13.481951987848586</v>
       </c>
       <c r="E55" s="57" t="s">
         <v>7</v>
@@ -3046,7 +3095,7 @@
       </c>
       <c r="N69" s="54">
         <f>5/384*qG*LL^4/(E*IncertieCM/100)*1000^2</f>
-        <v>15.675268118124157</v>
+        <v>14.711826640745972</v>
       </c>
       <c r="O69" t="s">
         <v>2</v>
@@ -3086,7 +3135,7 @@
       </c>
       <c r="N73" s="54">
         <f>N69+N70+Psi_0*N71</f>
-        <v>48.411981586632017</v>
+        <v>47.448540109253827</v>
       </c>
       <c r="O73" t="s">
         <v>2</v>
@@ -3122,7 +3171,7 @@
       </c>
       <c r="N78" s="56">
         <f>qG*LL/g*1000</f>
-        <v>11714.456259203738</v>
+        <v>10994.456259203738</v>
       </c>
       <c r="O78" t="s">
         <v>65</v>
@@ -3154,7 +3203,7 @@
       </c>
       <c r="N81" s="56">
         <f>N78+N80*N79</f>
-        <v>16607.422620060006</v>
+        <v>15887.422620060006</v>
       </c>
       <c r="O81" t="s">
         <v>65</v>
@@ -3170,7 +3219,7 @@
       </c>
       <c r="N83" s="56">
         <f>N81/2</f>
-        <v>8303.711310030003</v>
+        <v>7943.711310030003</v>
       </c>
       <c r="O83" t="s">
         <v>65</v>
@@ -3186,7 +3235,7 @@
       </c>
       <c r="N85" s="54">
         <f>1/2/PI()*SQRT(PI()^4*(E*IncertieCM/100)/N81/LL^3)</f>
-        <v>3.7659645751439088</v>
+        <v>3.8503536887793479</v>
       </c>
       <c r="O85" t="s">
         <v>78</v>
@@ -3200,23 +3249,23 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10702E5E-ED8A-4120-9F0B-C4375CB5FF62}">
-  <dimension ref="C2:K33"/>
+  <dimension ref="C2:S52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="4" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="6" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C6" s="4" t="s">
         <v>119</v>
       </c>
@@ -3233,7 +3282,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C7" s="4">
         <v>1</v>
       </c>
@@ -3247,11 +3296,11 @@
       </c>
       <c r="F7" s="78">
         <f t="shared" ref="F7:F12" si="1">MEd_U1*E7*1000</f>
-        <v>-687.00911233617398</v>
+        <v>-674.29247875363308</v>
       </c>
       <c r="G7" s="98">
         <f t="shared" ref="G7:G12" si="2">ABS(F7/(FyS/GammaM0))</f>
-        <v>1.9913307603947072</v>
+        <v>1.9544709529090813</v>
       </c>
       <c r="I7" s="75"/>
       <c r="J7" s="4"/>
@@ -3259,7 +3308,7 @@
         <v>-113.47</v>
       </c>
     </row>
-    <row r="8" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C8" s="4">
         <v>2</v>
       </c>
@@ -3273,17 +3322,17 @@
       </c>
       <c r="F8" s="78">
         <f t="shared" si="1"/>
-        <v>-633.8875006215286</v>
+        <v>-622.15415541079983</v>
       </c>
       <c r="G8" s="98">
         <f t="shared" si="2"/>
-        <v>1.8373550742653002</v>
+        <v>1.8033453780023183</v>
       </c>
       <c r="K8">
         <v>-138.15</v>
       </c>
     </row>
-    <row r="9" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C9" s="4">
         <v>3</v>
       </c>
@@ -3308,7 +3357,7 @@
         <v>-360.40950000000004</v>
       </c>
     </row>
-    <row r="10" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C10" s="4">
         <v>4</v>
       </c>
@@ -3322,18 +3371,18 @@
       </c>
       <c r="F10" s="78">
         <f t="shared" si="1"/>
-        <v>145.22947119327097</v>
+        <v>142.54125361742126</v>
       </c>
       <c r="G10" s="98">
         <f t="shared" si="2"/>
-        <v>0.42095498896600281</v>
+        <v>0.41316305396353992</v>
       </c>
       <c r="K10">
         <f>InertieY_MM4</f>
         <v>232737095.8107022</v>
       </c>
     </row>
-    <row r="11" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C11" s="4">
         <v>5</v>
       </c>
@@ -3346,14 +3395,14 @@
       </c>
       <c r="F11" s="78">
         <f t="shared" si="1"/>
-        <v>198.35108290791641</v>
+        <v>194.67957696025451</v>
       </c>
       <c r="G11" s="98">
         <f t="shared" si="2"/>
-        <v>0.57493067509540985</v>
-      </c>
-    </row>
-    <row r="12" spans="3:11" x14ac:dyDescent="0.25">
+        <v>0.56428862887030296</v>
+      </c>
+    </row>
+    <row r="12" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C12" s="4">
         <v>6</v>
       </c>
@@ -3367,79 +3416,126 @@
       </c>
       <c r="F12" s="78">
         <f t="shared" si="1"/>
-        <v>242.61909267012089</v>
+        <v>238.12817974594884</v>
       </c>
       <c r="G12" s="98">
         <f t="shared" si="2"/>
-        <v>0.70324374686991564</v>
-      </c>
-    </row>
-    <row r="13" spans="3:11" x14ac:dyDescent="0.25">
+        <v>0.69022660795927204</v>
+      </c>
+    </row>
+    <row r="13" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
     </row>
-    <row r="14" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
-    </row>
-    <row r="15" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="L14" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="M14" s="8">
+        <f>Ht-Pl_t</f>
+        <v>230</v>
+      </c>
+    </row>
+    <row r="15" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C15" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D15" s="48" t="e">
+      <c r="D15" s="48">
         <f>2/3*bAppMin</f>
-        <v>#REF!</v>
+        <v>33.333333333333329</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
     </row>
-    <row r="16" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C16" s="4"/>
     </row>
-    <row r="17" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="18" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="M17" s="104" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="19" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="L18" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="M18" s="54">
+        <f>dp</f>
+        <v>209.91666666666669</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C19" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D19" s="80" t="e">
-        <f>(Pl_b-bf)/2-dApp</f>
-        <v>#REF!</v>
+      <c r="D19" s="80">
+        <f>(Pl_b-tw)/2-dApp</f>
+        <v>209.91666666666669</v>
       </c>
       <c r="E19" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="20" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="L19" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="M19" s="54">
+        <f>qELU*M18/1000*1000/2</f>
+        <v>6633.4333344782217</v>
+      </c>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C20" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="D20" s="80" t="e">
+      <c r="D20" s="80">
         <f>qELU*dp*6/Pl_t^2/2</f>
-        <v>#REF!</v>
+        <v>99.501500017173328</v>
       </c>
       <c r="E20" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="22" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="L20" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="M20" s="5">
+        <f>Pl_t</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="L21" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="M21" s="5">
+        <f>FyPl</f>
+        <v>345</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="23" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="L22" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="M22" s="5">
+        <f>1.2*M20^2/6*M21/GammaM0</f>
+        <v>27600</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C23" s="3" t="s">
         <v>126</v>
       </c>
@@ -3450,20 +3546,38 @@
       <c r="E23" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="24" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="L23" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="M23" s="53">
+        <f>M19/M22</f>
+        <v>0.240341787481095</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C24" s="2" t="s">
         <v>127</v>
       </c>
       <c r="D24" s="80">
         <f>qELU*df*6/tf^2/2</f>
-        <v>38.987676868973892</v>
+        <v>38.266009583817642</v>
       </c>
       <c r="E24" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="27" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="L24" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="M24" s="53">
+        <f>(M23-SQRT(M23^2-16*M23+16))/(2*(M23-2))</f>
+        <v>0.92468744551869353</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="L25" s="3"/>
+      <c r="M25" s="5"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.25">
       <c r="D27" s="5" t="s">
         <v>134</v>
       </c>
@@ -3479,149 +3593,476 @@
       <c r="H27" s="5" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="28" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="M27" s="46" t="s">
+        <v>164</v>
+      </c>
+      <c r="N27" s="46"/>
+      <c r="O27" s="46"/>
+      <c r="P27" s="46"/>
+      <c r="Q27" s="46"/>
+      <c r="R27" s="46"/>
+      <c r="S27" s="46"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C28" s="3" t="s">
         <v>128</v>
       </c>
       <c r="D28" s="59">
         <f>F10</f>
-        <v>145.22947119327097</v>
+        <v>142.54125361742126</v>
       </c>
       <c r="E28" s="66">
         <f>+D24</f>
-        <v>38.987676868973892</v>
+        <v>38.266009583817642</v>
       </c>
       <c r="F28" s="4">
         <v>0</v>
       </c>
       <c r="G28" s="78">
         <f>SQRT(D28^2+E28^2-D28*E28+3*F28^2)</f>
-        <v>130.19016305382462</v>
+        <v>127.78032514937975</v>
       </c>
       <c r="H28" s="99">
         <f t="shared" ref="H28:H33" si="3">G28/(FyS/GammaM0)</f>
-        <v>0.37736279146036122</v>
-      </c>
-    </row>
-    <row r="29" spans="3:8" x14ac:dyDescent="0.25">
+        <v>0.37037775405617318</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C29" s="94" t="s">
         <v>129</v>
       </c>
       <c r="D29" s="59">
         <f>AVERAGE(D28,D30)</f>
-        <v>171.79027705059369</v>
+        <v>168.61041528883788</v>
       </c>
       <c r="E29" s="4">
         <v>0</v>
       </c>
       <c r="F29" s="75">
         <f>3/2*qELU/tf/2</f>
-        <v>2.0122671932373621</v>
+        <v>1.9750198494873625</v>
       </c>
       <c r="G29" s="78">
         <f t="shared" ref="G29:G33" si="4">SQRT(D29^2+E29^2-D29*E29+3*F29^2)</f>
-        <v>171.8256294820149</v>
+        <v>168.64511334186943</v>
       </c>
       <c r="H29" s="99">
         <f t="shared" si="3"/>
-        <v>0.49804530284642001</v>
-      </c>
-    </row>
-    <row r="30" spans="3:8" x14ac:dyDescent="0.25">
+        <v>0.4888264154836795</v>
+      </c>
+      <c r="M29" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N29" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="O29" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="P29" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q29" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="R29" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C30" s="3" t="s">
         <v>130</v>
       </c>
       <c r="D30" s="59">
         <f>F11</f>
-        <v>198.35108290791641</v>
+        <v>194.67957696025451</v>
       </c>
       <c r="E30" s="66">
         <f>-E28</f>
-        <v>-38.987676868973892</v>
+        <v>-38.266009583817642</v>
       </c>
       <c r="F30" s="4">
         <v>0</v>
       </c>
       <c r="G30" s="78">
         <f t="shared" si="4"/>
-        <v>220.44600011206268</v>
+        <v>216.36551419444629</v>
       </c>
       <c r="H30" s="99">
         <f t="shared" si="3"/>
-        <v>0.63897391336829756</v>
-      </c>
-    </row>
-    <row r="31" spans="3:8" x14ac:dyDescent="0.25">
+        <v>0.62714641795491677</v>
+      </c>
+      <c r="L30" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="M30" s="4">
+        <f>bf*tf</f>
+        <v>7200</v>
+      </c>
+      <c r="N30" s="4">
+        <f>FyS</f>
+        <v>345</v>
+      </c>
+      <c r="O30" s="4">
+        <f>M30*N30/1000</f>
+        <v>2484</v>
+      </c>
+      <c r="P30" s="4">
+        <f>zSup-tf/2</f>
+        <v>218</v>
+      </c>
+      <c r="Q30" s="4">
+        <f>O30</f>
+        <v>2484</v>
+      </c>
+      <c r="R30" s="105">
+        <f t="shared" ref="R30:R31" si="5">O30+R31</f>
+        <v>6741.5635568689422</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C31" s="3" t="s">
         <v>131</v>
       </c>
       <c r="D31" s="59">
         <f>F11</f>
-        <v>198.35108290791641</v>
-      </c>
-      <c r="E31" s="66" t="e">
+        <v>194.67957696025451</v>
+      </c>
+      <c r="E31" s="66">
         <f>D20</f>
-        <v>#REF!</v>
+        <v>99.501500017173328</v>
       </c>
       <c r="F31" s="4">
         <v>0</v>
       </c>
-      <c r="G31" s="78" t="e">
+      <c r="G31" s="78">
         <f t="shared" si="4"/>
-        <v>#REF!</v>
-      </c>
-      <c r="H31" s="99" t="e">
+        <v>168.61131711969142</v>
+      </c>
+      <c r="H31" s="99">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="32" spans="3:8" x14ac:dyDescent="0.25">
+        <v>0.48872845541939541</v>
+      </c>
+      <c r="L31" s="41" t="s">
+        <v>92</v>
+      </c>
+      <c r="M31" s="105">
+        <f>Feuil1!N19</f>
+        <v>312.88947776652043</v>
+      </c>
+      <c r="N31" s="4">
+        <f>FyW</f>
+        <v>345</v>
+      </c>
+      <c r="O31" s="105">
+        <f t="shared" ref="O31:O33" si="6">M31*N31/1000</f>
+        <v>107.94686982944954</v>
+      </c>
+      <c r="P31" s="59">
+        <f>zSup-tf-kcG*rr</f>
+        <v>199.96906564846469</v>
+      </c>
+      <c r="Q31" s="105">
+        <f>Q30+O31</f>
+        <v>2591.9468698294495</v>
+      </c>
+      <c r="R31" s="105">
+        <f t="shared" si="5"/>
+        <v>4257.5635568689422</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C32" s="3" t="s">
         <v>132</v>
       </c>
       <c r="D32" s="59">
         <f>AVERAGE(D31,D33)</f>
-        <v>220.48508778901865</v>
+        <v>216.40387835310167</v>
       </c>
       <c r="E32" s="4">
         <v>0</v>
       </c>
       <c r="F32" s="66">
         <f>3/2*qELU/Pl_t/2</f>
-        <v>2.4147206318848347</v>
+        <v>2.3700238193848349</v>
       </c>
       <c r="G32" s="78">
         <f t="shared" si="4"/>
-        <v>220.52475272522449</v>
+        <v>216.44280908585847</v>
       </c>
       <c r="H32" s="99">
         <f t="shared" si="3"/>
-        <v>0.63920218181224486</v>
-      </c>
-    </row>
-    <row r="33" spans="3:8" x14ac:dyDescent="0.25">
+        <v>0.62737046111843031</v>
+      </c>
+      <c r="L32" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="M32" s="105">
+        <f>Feuil1!N20</f>
+        <v>2781</v>
+      </c>
+      <c r="N32" s="4">
+        <f>FyW</f>
+        <v>345</v>
+      </c>
+      <c r="O32" s="105">
+        <f t="shared" si="6"/>
+        <v>959.44500000000005</v>
+      </c>
+      <c r="P32" s="4">
+        <f>hwP/2</f>
+        <v>103</v>
+      </c>
+      <c r="Q32" s="105">
+        <f t="shared" ref="Q32:Q33" si="7">Q31+O32</f>
+        <v>3551.3918698294497</v>
+      </c>
+      <c r="R32" s="105">
+        <f>O32+R33</f>
+        <v>4149.6166870394927</v>
+      </c>
+    </row>
+    <row r="33" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C33" s="3" t="s">
         <v>133</v>
       </c>
       <c r="D33" s="59">
         <f>F12</f>
-        <v>242.61909267012089</v>
-      </c>
-      <c r="E33" s="66" t="e">
+        <v>238.12817974594884</v>
+      </c>
+      <c r="E33" s="66">
         <f>-E31</f>
-        <v>#REF!</v>
+        <v>-99.501500017173328</v>
       </c>
       <c r="F33" s="4">
         <v>0</v>
       </c>
-      <c r="G33" s="78" t="e">
+      <c r="G33" s="78">
         <f t="shared" si="4"/>
-        <v>#REF!</v>
-      </c>
-      <c r="H33" s="99" t="e">
+        <v>300.49906751247573</v>
+      </c>
+      <c r="H33" s="99">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
+        <v>0.87101178989123396</v>
+      </c>
+      <c r="L33" s="41" t="s">
+        <v>89</v>
+      </c>
+      <c r="M33" s="4">
+        <f>Feuil1!N23</f>
+        <v>10000</v>
+      </c>
+      <c r="N33" s="105">
+        <f>FyPl*M24</f>
+        <v>319.01716870394927</v>
+      </c>
+      <c r="O33" s="105">
+        <f t="shared" si="6"/>
+        <v>3190.1716870394926</v>
+      </c>
+      <c r="P33" s="4">
+        <f>-Pl_t/2</f>
+        <v>-10</v>
+      </c>
+      <c r="Q33" s="105">
+        <f t="shared" si="7"/>
+        <v>6741.5635568689422</v>
+      </c>
+      <c r="R33" s="105">
+        <f>O33</f>
+        <v>3190.1716870394926</v>
+      </c>
+    </row>
+    <row r="34" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="M34" s="56">
+        <f>SUM(M30:M33)</f>
+        <v>20293.889477766519</v>
+      </c>
+      <c r="O34" s="56">
+        <f>SUM(O30:O33)</f>
+        <v>6741.5635568689422</v>
+      </c>
+    </row>
+    <row r="37" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="L37" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="38" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="L38" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M38" s="52">
+        <f>(SUM(O30:O32)-O33)/(2*O32)</f>
+        <v>0.18824434062919557</v>
+      </c>
+    </row>
+    <row r="39" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="L39" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="M39" s="53">
+        <f>pAnpLoc*(hwe)</f>
+        <v>38.77833416961429</v>
+      </c>
+      <c r="N39" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="M42" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="N42" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="O42" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="P42" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="43" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="L43" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="M43" s="4">
+        <f>O30</f>
+        <v>2484</v>
+      </c>
+      <c r="N43" s="4">
+        <f>P30</f>
+        <v>218</v>
+      </c>
+      <c r="O43" s="59">
+        <f>N43-zANPloc</f>
+        <v>179.22166583038572</v>
+      </c>
+      <c r="P43" s="106">
+        <f>M43*ABS(O43/1000)</f>
+        <v>445.18661792267812</v>
+      </c>
+    </row>
+    <row r="44" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="L44" s="41" t="s">
+        <v>92</v>
+      </c>
+      <c r="M44" s="105">
+        <f>O31</f>
+        <v>107.94686982944954</v>
+      </c>
+      <c r="N44" s="59">
+        <f>P31</f>
+        <v>199.96906564846469</v>
+      </c>
+      <c r="O44" s="59">
+        <f>N44-zANPloc</f>
+        <v>161.19073147885041</v>
+      </c>
+      <c r="P44" s="106">
+        <f t="shared" ref="P44:P47" si="8">M44*ABS(O44/1000)</f>
+        <v>17.400034908661219</v>
+      </c>
+    </row>
+    <row r="45" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="L45" s="41" t="s">
+        <v>153</v>
+      </c>
+      <c r="M45" s="105">
+        <f>(1-pAnpLoc)*O32</f>
+        <v>778.8349086050215</v>
+      </c>
+      <c r="N45" s="59">
+        <f>hwP-(1-pAnpLoc)*hwP/2</f>
+        <v>122.38916708480714</v>
+      </c>
+      <c r="O45" s="59">
+        <f>N45-zANPloc</f>
+        <v>83.610832915192844</v>
+      </c>
+      <c r="P45" s="106">
+        <f t="shared" si="8"/>
+        <v>65.119035411893947</v>
+      </c>
+    </row>
+    <row r="46" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="L46" s="41" t="s">
+        <v>154</v>
+      </c>
+      <c r="M46" s="105">
+        <f>(pAnpLoc)*O32</f>
+        <v>180.61009139497855</v>
+      </c>
+      <c r="N46" s="59">
+        <f>(pAnpLoc)*hwP/2</f>
+        <v>19.389167084807145</v>
+      </c>
+      <c r="O46" s="59">
+        <f>N46-zANPloc</f>
+        <v>-19.389167084807145</v>
+      </c>
+      <c r="P46" s="106">
+        <f t="shared" si="8"/>
+        <v>3.5018792392595284</v>
+      </c>
+    </row>
+    <row r="47" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="L47" s="41" t="s">
+        <v>89</v>
+      </c>
+      <c r="M47" s="105">
+        <f>O33</f>
+        <v>3190.1716870394926</v>
+      </c>
+      <c r="N47" s="105">
+        <f>P33</f>
+        <v>-10</v>
+      </c>
+      <c r="O47" s="59">
+        <f>N47-zANPloc</f>
+        <v>-48.77833416961429</v>
+      </c>
+      <c r="P47" s="106">
+        <f t="shared" si="8"/>
+        <v>155.61126060885454</v>
+      </c>
+    </row>
+    <row r="48" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="M48" s="56">
+        <f>SUM(M43:M47)</f>
+        <v>6741.5635568689422</v>
+      </c>
+      <c r="P48" s="56">
+        <f>SUM(P43:P47)</f>
+        <v>686.81882809134731</v>
+      </c>
+    </row>
+    <row r="50" spans="12:16" x14ac:dyDescent="0.25">
+      <c r="O50" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="P50" s="52">
+        <f>MEd_U1/'Flexion locale'!P48</f>
+        <v>0.73615495206185433</v>
+      </c>
+    </row>
+    <row r="51" spans="12:16" x14ac:dyDescent="0.25">
+      <c r="L51" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="M51" s="55">
+        <f>SUM(M43:M45)</f>
+        <v>3370.7817784344711</v>
+      </c>
+    </row>
+    <row r="52" spans="12:16" x14ac:dyDescent="0.25">
+      <c r="L52" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="M52" s="55">
+        <f>SUM(M46:M47)</f>
+        <v>3370.7817784344711</v>
       </c>
     </row>
   </sheetData>

--- a/VALIDATION/CAS SFS02/Cas SFS02.xlsx
+++ b/VALIDATION/CAS SFS02/Cas SFS02.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\RAID 1\LOGICIELS\CTICM AM - POUTRE MIXTE\DEV23\VALIDATION\CAS SFS02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48A03D8D-4A2E-4712-98CD-DA4CC2A9511D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30F6388F-5090-4AF6-9D40-E6B1F69E1FC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -947,7 +947,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1206,9 +1206,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3422,6 +3419,10 @@
         <f t="shared" si="2"/>
         <v>0.69022660795927204</v>
       </c>
+      <c r="M12">
+        <f>qELU</f>
+        <v>63.200635183595594</v>
+      </c>
     </row>
     <row r="13" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C13" s="4"/>
@@ -3939,7 +3940,7 @@
         <f>N43-zANPloc</f>
         <v>179.22166583038572</v>
       </c>
-      <c r="P43" s="106">
+      <c r="P43" s="59">
         <f>M43*ABS(O43/1000)</f>
         <v>445.18661792267812</v>
       </c>
@@ -3960,7 +3961,7 @@
         <f>N44-zANPloc</f>
         <v>161.19073147885041</v>
       </c>
-      <c r="P44" s="106">
+      <c r="P44" s="59">
         <f t="shared" ref="P44:P47" si="8">M44*ABS(O44/1000)</f>
         <v>17.400034908661219</v>
       </c>
@@ -3981,7 +3982,7 @@
         <f>N45-zANPloc</f>
         <v>83.610832915192844</v>
       </c>
-      <c r="P45" s="106">
+      <c r="P45" s="59">
         <f t="shared" si="8"/>
         <v>65.119035411893947</v>
       </c>
@@ -4002,7 +4003,7 @@
         <f>N46-zANPloc</f>
         <v>-19.389167084807145</v>
       </c>
-      <c r="P46" s="106">
+      <c r="P46" s="59">
         <f t="shared" si="8"/>
         <v>3.5018792392595284</v>
       </c>
@@ -4023,7 +4024,7 @@
         <f>N47-zANPloc</f>
         <v>-48.77833416961429</v>
       </c>
-      <c r="P47" s="106">
+      <c r="P47" s="59">
         <f t="shared" si="8"/>
         <v>155.61126060885454</v>
       </c>
